--- a/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117236</t>
+          <t>119603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161512</t>
+          <t>162147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>253500</t>
+          <t>257945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313708</t>
+          <t>312237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391569</t>
+          <t>390126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>456106</t>
+          <t>459794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>516591</t>
+          <t>515956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>560867</t>
+          <t>558500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>686381</t>
+          <t>687852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>746589</t>
+          <t>742144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1222086</t>
+          <t>1218398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286623</t>
+          <t>1288066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396380</t>
+          <t>396364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>458317</t>
+          <t>458834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>568276</t>
+          <t>568428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>629299</t>
+          <t>632516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>981377</t>
+          <t>987361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1071118</t>
+          <t>1070882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481891</t>
+          <t>481374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543828</t>
+          <t>543844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>381803</t>
+          <t>378586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442826</t>
+          <t>442674</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>880192</t>
+          <t>880428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>969933</t>
+          <t>963949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>121774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158280</t>
+          <t>157984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>157695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190820</t>
+          <t>190819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288939</t>
+          <t>291273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337979</t>
+          <t>337450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>133931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167953</t>
+          <t>170141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99352</t>
+          <t>99353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132173</t>
+          <t>132477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244107</t>
+          <t>244636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293147</t>
+          <t>290813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>663183</t>
+          <t>666019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>748468</t>
+          <t>749273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1010970</t>
+          <t>1015276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1103813</t>
+          <t>1109391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1698885</t>
+          <t>1698777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1829024</t>
+          <t>1830993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1161758</t>
+          <t>1160953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1247043</t>
+          <t>1244207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1197549</t>
+          <t>1191971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1290392</t>
+          <t>1286086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2382564</t>
+          <t>2380595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2512703</t>
+          <t>2512811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174575</t>
+          <t>174118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225111</t>
+          <t>224416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361013</t>
+          <t>361559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>423981</t>
+          <t>424244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>553251</t>
+          <t>553089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>635527</t>
+          <t>636153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>491887</t>
+          <t>492582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>542423</t>
+          <t>542880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638330</t>
+          <t>638067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>701298</t>
+          <t>700752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143782</t>
+          <t>1143156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1226058</t>
+          <t>1226220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>637106</t>
+          <t>640079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>709917</t>
+          <t>707484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>902090</t>
+          <t>898844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>959797</t>
+          <t>957522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1551100</t>
+          <t>1555089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1649712</t>
+          <t>1648094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448254</t>
+          <t>450687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>521065</t>
+          <t>518092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223088</t>
+          <t>225363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>280795</t>
+          <t>284041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691344</t>
+          <t>692962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789956</t>
+          <t>785967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163473</t>
+          <t>163540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194866</t>
+          <t>194812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212235</t>
+          <t>211000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238435</t>
+          <t>238499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384913</t>
+          <t>385097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>427184</t>
+          <t>427014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>64766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96105</t>
+          <t>96038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56289</t>
+          <t>57524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100917</t>
+          <t>101087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143188</t>
+          <t>143004</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1006086</t>
+          <t>1004199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1097432</t>
+          <t>1101425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1499626</t>
+          <t>1500332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1598359</t>
+          <t>1600399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2534906</t>
+          <t>2536806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2676913</t>
+          <t>2674204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1037314</t>
+          <t>1033321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128660</t>
+          <t>1130547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>915361</t>
+          <t>913321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014094</t>
+          <t>1013388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1971553</t>
+          <t>1974262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2113560</t>
+          <t>2111660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119805</t>
+          <t>121511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161919</t>
+          <t>163452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197418</t>
+          <t>196765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247952</t>
+          <t>247788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330668</t>
+          <t>333325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>397722</t>
+          <t>400996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356331</t>
+          <t>354798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398445</t>
+          <t>396739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>537607</t>
+          <t>537771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>588141</t>
+          <t>588794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906088</t>
+          <t>902814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>973142</t>
+          <t>970485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>510333</t>
+          <t>503990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>574902</t>
+          <t>572281</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>713802</t>
+          <t>714198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>783953</t>
+          <t>787049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1244599</t>
+          <t>1238267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1339902</t>
+          <t>1340667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>527040</t>
+          <t>529661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>591609</t>
+          <t>597952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448592</t>
+          <t>445496</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518743</t>
+          <t>518347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994585</t>
+          <t>993820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1089888</t>
+          <t>1096220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133288</t>
+          <t>134299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166926</t>
+          <t>167537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204423</t>
+          <t>205020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238076</t>
+          <t>238355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347084</t>
+          <t>349653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>398271</t>
+          <t>397831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101403</t>
+          <t>100792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135041</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>74065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107997</t>
+          <t>107400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182478</t>
+          <t>182918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>233665</t>
+          <t>231096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>791261</t>
+          <t>787034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>873248</t>
+          <t>873374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1144915</t>
+          <t>1143470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1243104</t>
+          <t>1245192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1958406</t>
+          <t>1959385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2094518</t>
+          <t>2091070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1015273</t>
+          <t>1015147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1097260</t>
+          <t>1101487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1087420</t>
+          <t>1085332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1185609</t>
+          <t>1187054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2124527</t>
+          <t>2127975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2260639</t>
+          <t>2259660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>59525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68419</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94024</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109612</t>
+          <t>109436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144725</t>
+          <t>144843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454721</t>
+          <t>455413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479583</t>
+          <t>479227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661484</t>
+          <t>660663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687089</t>
+          <t>685473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1125721</t>
+          <t>1125603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1160834</t>
+          <t>1161010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123129</t>
+          <t>121446</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209683</t>
+          <t>209820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277409</t>
+          <t>279658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>959667</t>
+          <t>909568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>440886</t>
+          <t>436733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1276954</t>
+          <t>1287495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2080644</t>
+          <t>2080507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2167198</t>
+          <t>2168881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1278156</t>
+          <t>1328255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1960414</t>
+          <t>1958165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3251196</t>
+          <t>3240655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4087264</t>
+          <t>4091417</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63715</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>55179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>80709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95157</t>
+          <t>93172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135375</t>
+          <t>134055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582908</t>
+          <t>583080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612937</t>
+          <t>612739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579811</t>
+          <t>579754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606655</t>
+          <t>605284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171711</t>
+          <t>1173031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1211929</t>
+          <t>1213914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211633</t>
+          <t>204801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308238</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>424655</t>
+          <t>425823</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1204557</t>
+          <t>1177672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>677673</t>
+          <t>671468</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1551083</t>
+          <t>1555376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3143651</t>
+          <t>3144278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3240256</t>
+          <t>3247088</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2449237</t>
+          <t>2476122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3229139</t>
+          <t>3227971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5554600</t>
+          <t>5550307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6428010</t>
+          <t>6434215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119603</t>
+          <t>118817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162147</t>
+          <t>163824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>257945</t>
+          <t>257975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>312237</t>
+          <t>313756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>390126</t>
+          <t>389061</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>459794</t>
+          <t>459718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>515956</t>
+          <t>514279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>558500</t>
+          <t>559286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687852</t>
+          <t>686333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>742144</t>
+          <t>742114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1218398</t>
+          <t>1218474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1288066</t>
+          <t>1289131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396364</t>
+          <t>396217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>458834</t>
+          <t>459417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>568428</t>
+          <t>566145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>632516</t>
+          <t>629813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>987361</t>
+          <t>982049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1070882</t>
+          <t>1068459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481374</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543844</t>
+          <t>543991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378586</t>
+          <t>381289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>444957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>880428</t>
+          <t>882851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963949</t>
+          <t>969261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121774</t>
+          <t>123585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157984</t>
+          <t>157685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>54,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>174472</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>157269</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>192927</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>60,13%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>54,2%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>315026</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>290596</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>338577</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>54,12%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>174472</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>157695</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>190819</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>60,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>54,35%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>315026</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>291273</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>337450</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>54,12%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133931</t>
+          <t>134230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170141</t>
+          <t>168330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>45,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>115700</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>97245</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>132903</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>39,87%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>267060</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>243509</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>291490</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>45,88%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115700</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>99353</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132477</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>45,65%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>267060</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>244636</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>290813</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>45,88%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>666019</t>
+          <t>664139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>749273</t>
+          <t>750667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1015276</t>
+          <t>1014719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1109391</t>
+          <t>1108578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1698777</t>
+          <t>1695103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1830993</t>
+          <t>1826314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1160953</t>
+          <t>1159559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1244207</t>
+          <t>1246087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1191971</t>
+          <t>1192784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1286086</t>
+          <t>1286643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2380595</t>
+          <t>2385274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2512811</t>
+          <t>2516485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174118</t>
+          <t>173915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224416</t>
+          <t>225440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>361559</t>
+          <t>361555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424244</t>
+          <t>424141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>553089</t>
+          <t>553379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636153</t>
+          <t>636503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492582</t>
+          <t>491558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>542880</t>
+          <t>543083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638067</t>
+          <t>638170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700752</t>
+          <t>700756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143156</t>
+          <t>1142806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1226220</t>
+          <t>1225930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>640079</t>
+          <t>638504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>707337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>898844</t>
+          <t>903658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>957522</t>
+          <t>959117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1555089</t>
+          <t>1554953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1648094</t>
+          <t>1649826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450687</t>
+          <t>450834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>518092</t>
+          <t>519667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225363</t>
+          <t>223768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>284041</t>
+          <t>279227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692962</t>
+          <t>691230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785967</t>
+          <t>786103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163540</t>
+          <t>162048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194812</t>
+          <t>196077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211000</t>
+          <t>212620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238499</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>385097</t>
+          <t>384946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>427014</t>
+          <t>427891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64766</t>
+          <t>63501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96038</t>
+          <t>97530</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101087</t>
+          <t>100210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143004</t>
+          <t>143155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1004199</t>
+          <t>1009029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1101425</t>
+          <t>1099527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1500332</t>
+          <t>1498479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1600399</t>
+          <t>1595453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2536806</t>
+          <t>2529743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2674204</t>
+          <t>2669451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1033321</t>
+          <t>1035219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1130547</t>
+          <t>1125717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913321</t>
+          <t>918267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1013388</t>
+          <t>1015241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1974262</t>
+          <t>1979015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2111660</t>
+          <t>2118723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121511</t>
+          <t>121452</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163452</t>
+          <t>162208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196765</t>
+          <t>196178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>248138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>333325</t>
+          <t>329381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400996</t>
+          <t>397054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354798</t>
+          <t>356042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396739</t>
+          <t>396798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>537771</t>
+          <t>537421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>588794</t>
+          <t>589381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902814</t>
+          <t>906756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>970485</t>
+          <t>974429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503990</t>
+          <t>504051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>572281</t>
+          <t>573430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>714198</t>
+          <t>713278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>787049</t>
+          <t>783599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1238267</t>
+          <t>1242933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1340667</t>
+          <t>1337966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>529661</t>
+          <t>528512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>597952</t>
+          <t>597891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445496</t>
+          <t>448946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518347</t>
+          <t>519267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993820</t>
+          <t>996521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1096220</t>
+          <t>1091554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134299</t>
+          <t>130642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167537</t>
+          <t>166493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205020</t>
+          <t>204584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238355</t>
+          <t>238364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349653</t>
+          <t>349188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>397831</t>
+          <t>397279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134030</t>
+          <t>137687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74065</t>
+          <t>74056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>107836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182918</t>
+          <t>183470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231096</t>
+          <t>231561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>787034</t>
+          <t>789286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>873374</t>
+          <t>881874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1143470</t>
+          <t>1140340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1245192</t>
+          <t>1240418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1959385</t>
+          <t>1965320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2091070</t>
+          <t>2094132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1015147</t>
+          <t>1006647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1101487</t>
+          <t>1099235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1085332</t>
+          <t>1090106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1187054</t>
+          <t>1190184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2127975</t>
+          <t>2124913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2259660</t>
+          <t>2253725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>41873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59525</t>
+          <t>68023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>80779</t>
+          <t>94762</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>81196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>127039</t>
+          <t>147533</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109436</t>
+          <t>128568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144843</t>
+          <t>166780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>468677</t>
+          <t>525758</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455413</t>
+          <t>510506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>479227</t>
+          <t>536656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>674729</t>
+          <t>727276</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660663</t>
+          <t>710992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685473</t>
+          <t>740842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1143407</t>
+          <t>1253034</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1125603</t>
+          <t>1233787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1161010</t>
+          <t>1271999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>174242</t>
+          <t>206841</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121446</t>
+          <t>177547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209820</t>
+          <t>235979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>469960</t>
+          <t>307610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279658</t>
+          <t>281143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>909568</t>
+          <t>343566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>644202</t>
+          <t>514452</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>436733</t>
+          <t>472106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1287495</t>
+          <t>559858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2116085</t>
+          <t>2023725</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2080507</t>
+          <t>1994587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2168881</t>
+          <t>2053019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1767863</t>
+          <t>1863782</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1328255</t>
+          <t>1827826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1958165</t>
+          <t>1890249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3883948</t>
+          <t>3887507</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3240655</t>
+          <t>3842101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4091417</t>
+          <t>3929853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66435</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55179</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>93929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>131894</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93172</t>
+          <t>111753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134055</t>
+          <t>156162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>599610</t>
+          <t>657959</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583080</t>
+          <t>640177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612739</t>
+          <t>673222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>594028</t>
+          <t>656611</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579754</t>
+          <t>640948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605284</t>
+          <t>671312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1193638</t>
+          <t>1314570</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1173031</t>
+          <t>1290302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1213914</t>
+          <t>1334711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313240</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204801</t>
+          <t>278291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307611</t>
+          <t>353270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>425823</t>
+          <t>445487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1177672</t>
+          <t>520734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>671468</t>
+          <t>739045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1555376</t>
+          <t>840926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3184373</t>
+          <t>3207443</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3144278</t>
+          <t>3167413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3247088</t>
+          <t>3242392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3036620</t>
+          <t>3247669</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2476122</t>
+          <t>3207573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3227971</t>
+          <t>3282820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6220993</t>
+          <t>6455112</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5550307</t>
+          <t>6408064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6434215</t>
+          <t>6509945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
